--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-24T19:48:18+00:00</t>
+    <t>2024-10-29T08:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4758" uniqueCount="688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4758" uniqueCount="691">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T08:42:45+00:00</t>
+    <t>2024-10-29T10:21:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,14 +455,17 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Encounter.extension:Unfalldatum</t>
-  </si>
-  <si>
-    <t>Unfalldatum</t>
+    <t>Encounter.extension:unfalldatum</t>
+  </si>
+  <si>
+    <t>unfalldatum</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-unfalldatum}
 </t>
+  </si>
+  <si>
+    <t>Unfalldatum</t>
   </si>
   <si>
     <t>MOPED Extension für das Ereignis-/Unfalldatum.</t>
@@ -1952,27 +1955,33 @@
     <t>Encounter.admission.extension</t>
   </si>
   <si>
-    <t>Encounter.admission.extension:Zugangsart</t>
-  </si>
-  <si>
-    <t>Zugangsart</t>
+    <t>Encounter.admission.extension:zugangsart</t>
+  </si>
+  <si>
+    <t>zugangsart</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-zugangsart}
 </t>
   </si>
   <si>
+    <t>Zugangsart</t>
+  </si>
+  <si>
     <t>MOPED Extension für die Art des Zugangs.</t>
   </si>
   <si>
-    <t>Encounter.admission.extension:Transportart</t>
-  </si>
-  <si>
-    <t>Transportart</t>
+    <t>Encounter.admission.extension:transportart</t>
+  </si>
+  <si>
+    <t>transportart</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-transportart}
 </t>
+  </si>
+  <si>
+    <t>Transportart</t>
   </si>
   <si>
     <t>MOPED Extension für die Transportart.</t>
@@ -3572,10 +3581,10 @@
         <v>143</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3655,14 +3664,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3684,16 +3693,16 @@
         <v>134</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>19</v>
@@ -3742,7 +3751,7 @@
         <v>19</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -3771,10 +3780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3797,13 +3806,13 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3842,7 +3851,7 @@
         <v>19</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AC12" s="2"/>
       <c r="AD12" t="s" s="2">
@@ -3852,7 +3861,7 @@
         <v>138</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -3867,27 +3876,27 @@
         <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>19</v>
@@ -3909,13 +3918,13 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3966,7 +3975,7 @@
         <v>19</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3981,24 +3990,24 @@
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4024,10 +4033,10 @@
         <v>89</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4078,7 +4087,7 @@
         <v>19</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -4087,7 +4096,7 @@
         <v>87</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>19</v>
@@ -4099,7 +4108,7 @@
         <v>19</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>19</v>
@@ -4107,14 +4116,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4136,13 +4145,13 @@
         <v>134</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4183,7 +4192,7 @@
         <v>137</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>19</v>
@@ -4192,7 +4201,7 @@
         <v>138</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -4213,7 +4222,7 @@
         <v>19</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>19</v>
@@ -4221,10 +4230,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4250,16 +4259,16 @@
         <v>107</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>19</v>
@@ -4287,10 +4296,10 @@
         <v>111</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>19</v>
@@ -4308,7 +4317,7 @@
         <v>19</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -4329,7 +4338,7 @@
         <v>19</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>132</v>
@@ -4337,10 +4346,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4363,19 +4372,19 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>19</v>
@@ -4404,7 +4413,7 @@
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>19</v>
@@ -4422,7 +4431,7 @@
         <v>19</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -4443,18 +4452,18 @@
         <v>19</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4480,10 +4489,10 @@
         <v>89</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4534,7 +4543,7 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -4543,7 +4552,7 @@
         <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>19</v>
@@ -4555,7 +4564,7 @@
         <v>19</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>19</v>
@@ -4563,14 +4572,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4592,13 +4601,13 @@
         <v>134</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4639,7 +4648,7 @@
         <v>137</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>19</v>
@@ -4648,7 +4657,7 @@
         <v>138</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -4669,7 +4678,7 @@
         <v>19</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>19</v>
@@ -4677,10 +4686,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4703,19 +4712,19 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>19</v>
@@ -4764,7 +4773,7 @@
         <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -4785,18 +4794,18 @@
         <v>19</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4822,10 +4831,10 @@
         <v>89</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4876,7 +4885,7 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -4885,7 +4894,7 @@
         <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>19</v>
@@ -4897,7 +4906,7 @@
         <v>19</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>19</v>
@@ -4905,14 +4914,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4934,13 +4943,13 @@
         <v>134</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4981,7 +4990,7 @@
         <v>137</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>19</v>
@@ -4990,7 +4999,7 @@
         <v>138</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -5011,7 +5020,7 @@
         <v>19</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>19</v>
@@ -5019,10 +5028,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5048,16 +5057,16 @@
         <v>101</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>19</v>
@@ -5106,7 +5115,7 @@
         <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -5127,18 +5136,18 @@
         <v>19</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5161,16 +5170,16 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5220,7 +5229,7 @@
         <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -5241,18 +5250,18 @@
         <v>19</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5278,21 +5287,21 @@
         <v>107</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>19</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>19</v>
@@ -5334,7 +5343,7 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -5343,7 +5352,7 @@
         <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>99</v>
@@ -5355,18 +5364,18 @@
         <v>19</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5389,17 +5398,17 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>19</v>
@@ -5448,7 +5457,7 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -5457,7 +5466,7 @@
         <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>99</v>
@@ -5469,18 +5478,18 @@
         <v>19</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5503,19 +5512,19 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>19</v>
@@ -5564,7 +5573,7 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -5585,18 +5594,18 @@
         <v>19</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5619,19 +5628,19 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>19</v>
@@ -5680,7 +5689,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -5701,18 +5710,18 @@
         <v>19</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5738,16 +5747,16 @@
         <v>101</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>19</v>
@@ -5760,7 +5769,7 @@
         <v>19</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>19</v>
@@ -5796,7 +5805,7 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5817,18 +5826,18 @@
         <v>19</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5851,16 +5860,16 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5874,7 +5883,7 @@
         <v>19</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>19</v>
@@ -5910,7 +5919,7 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5919,7 +5928,7 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
@@ -5931,18 +5940,18 @@
         <v>19</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5965,13 +5974,13 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6022,7 +6031,7 @@
         <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -6043,18 +6052,18 @@
         <v>19</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6077,16 +6086,16 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6136,7 +6145,7 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -6157,21 +6166,21 @@
         <v>19</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>19</v>
@@ -6193,13 +6202,13 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6250,7 +6259,7 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -6265,24 +6274,24 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6308,10 +6317,10 @@
         <v>89</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6362,7 +6371,7 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -6371,7 +6380,7 @@
         <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>19</v>
@@ -6383,7 +6392,7 @@
         <v>19</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>19</v>
@@ -6391,14 +6400,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6420,13 +6429,13 @@
         <v>134</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6467,7 +6476,7 @@
         <v>137</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>19</v>
@@ -6476,7 +6485,7 @@
         <v>138</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -6497,7 +6506,7 @@
         <v>19</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>19</v>
@@ -6505,10 +6514,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6534,16 +6543,16 @@
         <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>19</v>
@@ -6571,10 +6580,10 @@
         <v>111</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>19</v>
@@ -6592,7 +6601,7 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -6613,7 +6622,7 @@
         <v>19</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>132</v>
@@ -6621,10 +6630,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6647,19 +6656,19 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>19</v>
@@ -6688,7 +6697,7 @@
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>19</v>
@@ -6706,7 +6715,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -6727,18 +6736,18 @@
         <v>19</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6764,10 +6773,10 @@
         <v>89</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6818,7 +6827,7 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6827,7 +6836,7 @@
         <v>87</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>19</v>
@@ -6839,7 +6848,7 @@
         <v>19</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>19</v>
@@ -6847,14 +6856,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6876,13 +6885,13 @@
         <v>134</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6923,7 +6932,7 @@
         <v>137</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>19</v>
@@ -6932,7 +6941,7 @@
         <v>138</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6953,7 +6962,7 @@
         <v>19</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>19</v>
@@ -6961,10 +6970,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6987,19 +6996,19 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>19</v>
@@ -7048,7 +7057,7 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -7069,18 +7078,18 @@
         <v>19</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7106,10 +7115,10 @@
         <v>89</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7160,7 +7169,7 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -7169,7 +7178,7 @@
         <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>19</v>
@@ -7181,7 +7190,7 @@
         <v>19</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>19</v>
@@ -7189,14 +7198,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7218,13 +7227,13 @@
         <v>134</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7265,7 +7274,7 @@
         <v>137</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>19</v>
@@ -7274,7 +7283,7 @@
         <v>138</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -7295,7 +7304,7 @@
         <v>19</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>19</v>
@@ -7303,10 +7312,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7332,16 +7341,16 @@
         <v>101</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>19</v>
@@ -7390,7 +7399,7 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -7411,18 +7420,18 @@
         <v>19</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7445,16 +7454,16 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7504,7 +7513,7 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -7525,18 +7534,18 @@
         <v>19</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7562,21 +7571,21 @@
         <v>107</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>19</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>19</v>
@@ -7618,7 +7627,7 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -7627,7 +7636,7 @@
         <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>99</v>
@@ -7639,18 +7648,18 @@
         <v>19</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7673,17 +7682,17 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>19</v>
@@ -7732,7 +7741,7 @@
         <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7741,7 +7750,7 @@
         <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>99</v>
@@ -7753,18 +7762,18 @@
         <v>19</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7787,19 +7796,19 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>19</v>
@@ -7848,7 +7857,7 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7869,18 +7878,18 @@
         <v>19</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7903,19 +7912,19 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>19</v>
@@ -7964,7 +7973,7 @@
         <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7985,18 +7994,18 @@
         <v>19</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8022,16 +8031,16 @@
         <v>101</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -8044,7 +8053,7 @@
         <v>19</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>19</v>
@@ -8080,7 +8089,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -8101,18 +8110,18 @@
         <v>19</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8135,16 +8144,16 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8158,7 +8167,7 @@
         <v>19</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>19</v>
@@ -8194,7 +8203,7 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -8203,7 +8212,7 @@
         <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>99</v>
@@ -8215,18 +8224,18 @@
         <v>19</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8249,13 +8258,13 @@
         <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8306,7 +8315,7 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -8327,18 +8336,18 @@
         <v>19</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8361,16 +8370,16 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8420,7 +8429,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -8441,18 +8450,18 @@
         <v>19</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8478,13 +8487,13 @@
         <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8513,10 +8522,10 @@
         <v>111</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>19</v>
@@ -8534,7 +8543,7 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>87</v>
@@ -8549,24 +8558,24 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8589,13 +8598,13 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8622,19 +8631,19 @@
         <v>19</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AC54" s="2"/>
       <c r="AD54" t="s" s="2">
@@ -8644,7 +8653,7 @@
         <v>138</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -8662,24 +8671,24 @@
         <v>19</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>19</v>
@@ -8701,13 +8710,13 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8738,7 +8747,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>19</v>
@@ -8756,7 +8765,7 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8774,24 +8783,24 @@
         <v>19</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>19</v>
@@ -8813,13 +8822,13 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8850,7 +8859,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>19</v>
@@ -8868,7 +8877,7 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8886,21 +8895,21 @@
         <v>19</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8923,13 +8932,13 @@
         <v>19</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8956,13 +8965,13 @@
         <v>19</v>
       </c>
       <c r="X57" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="Y57" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="Y57" t="s" s="2">
-        <v>358</v>
-      </c>
       <c r="Z57" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>19</v>
@@ -8980,7 +8989,7 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8998,21 +9007,21 @@
         <v>19</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9035,16 +9044,16 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9070,13 +9079,13 @@
         <v>19</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>19</v>
@@ -9094,7 +9103,7 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -9109,24 +9118,24 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9149,13 +9158,13 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9182,13 +9191,13 @@
         <v>19</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>19</v>
@@ -9206,7 +9215,7 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -9221,28 +9230,28 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9261,16 +9270,16 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9320,7 +9329,7 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -9335,24 +9344,24 @@
         <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9375,16 +9384,16 @@
         <v>19</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9410,13 +9419,13 @@
         <v>19</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>19</v>
@@ -9434,7 +9443,7 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -9463,10 +9472,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9489,13 +9498,13 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9546,7 +9555,7 @@
         <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -9564,25 +9573,25 @@
         <v>19</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9601,13 +9610,13 @@
         <v>19</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9658,7 +9667,7 @@
         <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -9673,13 +9682,13 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>19</v>
@@ -9687,10 +9696,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9713,13 +9722,13 @@
         <v>19</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9770,7 +9779,7 @@
         <v>19</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -9791,7 +9800,7 @@
         <v>19</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>19</v>
@@ -9799,10 +9808,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9825,16 +9834,16 @@
         <v>19</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9884,7 +9893,7 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9899,13 +9908,13 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>19</v>
@@ -9913,10 +9922,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9939,13 +9948,13 @@
         <v>19</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9996,7 +10005,7 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -10011,24 +10020,24 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10051,16 +10060,16 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10110,7 +10119,7 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -10122,27 +10131,27 @@
         <v>19</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10165,13 +10174,13 @@
         <v>19</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10222,7 +10231,7 @@
         <v>19</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -10231,7 +10240,7 @@
         <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>19</v>
@@ -10243,7 +10252,7 @@
         <v>19</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>19</v>
@@ -10251,14 +10260,14 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10280,13 +10289,13 @@
         <v>134</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10336,7 +10345,7 @@
         <v>19</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -10357,7 +10366,7 @@
         <v>19</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>19</v>
@@ -10365,14 +10374,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10394,16 +10403,16 @@
         <v>134</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>19</v>
@@ -10452,7 +10461,7 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -10481,10 +10490,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10507,16 +10516,16 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10542,13 +10551,13 @@
         <v>19</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>19</v>
@@ -10566,7 +10575,7 @@
         <v>19</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -10575,30 +10584,30 @@
         <v>78</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10621,13 +10630,13 @@
         <v>19</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10678,7 +10687,7 @@
         <v>19</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -10699,18 +10708,18 @@
         <v>19</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10733,16 +10742,16 @@
         <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10792,7 +10801,7 @@
         <v>19</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -10801,30 +10810,30 @@
         <v>87</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10847,13 +10856,13 @@
         <v>88</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10904,7 +10913,7 @@
         <v>19</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10919,24 +10928,24 @@
         <v>99</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10959,16 +10968,16 @@
         <v>19</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11018,7 +11027,7 @@
         <v>19</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -11047,10 +11056,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11073,16 +11082,16 @@
         <v>19</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11132,7 +11141,7 @@
         <v>19</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
@@ -11147,24 +11156,24 @@
         <v>99</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11187,13 +11196,13 @@
         <v>19</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11244,7 +11253,7 @@
         <v>19</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -11268,15 +11277,15 @@
         <v>19</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11299,13 +11308,13 @@
         <v>19</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11356,7 +11365,7 @@
         <v>19</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -11380,15 +11389,15 @@
         <v>19</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11411,16 +11420,16 @@
         <v>19</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11470,7 +11479,7 @@
         <v>19</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
@@ -11485,24 +11494,24 @@
         <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11525,16 +11534,16 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11572,7 +11581,7 @@
         <v>19</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AC80" s="2"/>
       <c r="AD80" t="s" s="2">
@@ -11582,7 +11591,7 @@
         <v>138</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -11611,10 +11620,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11637,13 +11646,13 @@
         <v>19</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11694,7 +11703,7 @@
         <v>19</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -11703,7 +11712,7 @@
         <v>87</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>19</v>
@@ -11715,7 +11724,7 @@
         <v>19</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>19</v>
@@ -11723,14 +11732,14 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11752,13 +11761,13 @@
         <v>134</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11808,7 +11817,7 @@
         <v>19</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -11829,7 +11838,7 @@
         <v>19</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>19</v>
@@ -11837,14 +11846,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -11866,16 +11875,16 @@
         <v>134</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>19</v>
@@ -11924,7 +11933,7 @@
         <v>19</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
@@ -11953,10 +11962,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11979,13 +11988,13 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12012,11 +12021,11 @@
         <v>19</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>19</v>
@@ -12034,7 +12043,7 @@
         <v>19</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
@@ -12063,14 +12072,14 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12089,13 +12098,13 @@
         <v>88</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12122,13 +12131,13 @@
         <v>19</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>19</v>
@@ -12146,7 +12155,7 @@
         <v>19</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
@@ -12161,27 +12170,27 @@
         <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>19</v>
@@ -12203,16 +12212,16 @@
         <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12262,7 +12271,7 @@
         <v>19</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
@@ -12291,10 +12300,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12317,13 +12326,13 @@
         <v>19</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12374,7 +12383,7 @@
         <v>19</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>77</v>
@@ -12383,7 +12392,7 @@
         <v>87</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>19</v>
@@ -12395,7 +12404,7 @@
         <v>19</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>19</v>
@@ -12403,14 +12412,14 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12432,13 +12441,13 @@
         <v>134</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12488,7 +12497,7 @@
         <v>19</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
@@ -12509,7 +12518,7 @@
         <v>19</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>19</v>
@@ -12517,14 +12526,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12546,16 +12555,16 @@
         <v>134</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>19</v>
@@ -12604,7 +12613,7 @@
         <v>19</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -12633,10 +12642,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12659,13 +12668,13 @@
         <v>88</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12696,7 +12705,7 @@
       </c>
       <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>19</v>
@@ -12714,7 +12723,7 @@
         <v>19</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
@@ -12743,10 +12752,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12772,10 +12781,10 @@
         <v>89</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12826,7 +12835,7 @@
         <v>19</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
@@ -12835,7 +12844,7 @@
         <v>87</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>19</v>
@@ -12847,7 +12856,7 @@
         <v>19</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>19</v>
@@ -12855,14 +12864,14 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -12884,13 +12893,13 @@
         <v>134</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12931,7 +12940,7 @@
         <v>137</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>19</v>
@@ -12940,7 +12949,7 @@
         <v>138</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>77</v>
@@ -12961,7 +12970,7 @@
         <v>19</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>19</v>
@@ -12969,10 +12978,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12995,19 +13004,19 @@
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>19</v>
@@ -13056,7 +13065,7 @@
         <v>19</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>77</v>
@@ -13077,18 +13086,18 @@
         <v>19</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13114,10 +13123,10 @@
         <v>89</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13168,7 +13177,7 @@
         <v>19</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>77</v>
@@ -13177,7 +13186,7 @@
         <v>87</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>19</v>
@@ -13189,7 +13198,7 @@
         <v>19</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>19</v>
@@ -13197,14 +13206,14 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13226,13 +13235,13 @@
         <v>134</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13273,7 +13282,7 @@
         <v>137</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>19</v>
@@ -13282,7 +13291,7 @@
         <v>138</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -13303,7 +13312,7 @@
         <v>19</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>19</v>
@@ -13311,10 +13320,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13340,16 +13349,16 @@
         <v>101</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>19</v>
@@ -13398,7 +13407,7 @@
         <v>19</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>77</v>
@@ -13419,18 +13428,18 @@
         <v>19</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13453,16 +13462,16 @@
         <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13512,7 +13521,7 @@
         <v>19</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>77</v>
@@ -13533,18 +13542,18 @@
         <v>19</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13570,21 +13579,21 @@
         <v>107</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>19</v>
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="S98" t="s" s="2">
         <v>19</v>
@@ -13626,7 +13635,7 @@
         <v>19</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>77</v>
@@ -13635,7 +13644,7 @@
         <v>87</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>99</v>
@@ -13647,18 +13656,18 @@
         <v>19</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13681,17 +13690,17 @@
         <v>88</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>19</v>
@@ -13740,7 +13749,7 @@
         <v>19</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>77</v>
@@ -13749,7 +13758,7 @@
         <v>87</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>99</v>
@@ -13761,18 +13770,18 @@
         <v>19</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13795,19 +13804,19 @@
         <v>88</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>19</v>
@@ -13856,7 +13865,7 @@
         <v>19</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>77</v>
@@ -13877,18 +13886,18 @@
         <v>19</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13911,19 +13920,19 @@
         <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>19</v>
@@ -13972,7 +13981,7 @@
         <v>19</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>77</v>
@@ -13993,22 +14002,22 @@
         <v>19</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14027,13 +14036,13 @@
         <v>88</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14064,7 +14073,7 @@
       </c>
       <c r="Y102" s="2"/>
       <c r="Z102" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>19</v>
@@ -14082,7 +14091,7 @@
         <v>19</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
@@ -14097,24 +14106,24 @@
         <v>99</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14137,16 +14146,16 @@
         <v>88</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14196,7 +14205,7 @@
         <v>19</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
@@ -14217,7 +14226,7 @@
         <v>19</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>19</v>
@@ -14225,10 +14234,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14251,13 +14260,13 @@
         <v>19</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14308,7 +14317,7 @@
         <v>19</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
@@ -14317,7 +14326,7 @@
         <v>87</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>19</v>
@@ -14329,7 +14338,7 @@
         <v>19</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>19</v>
@@ -14337,14 +14346,14 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -14366,13 +14375,13 @@
         <v>134</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14422,7 +14431,7 @@
         <v>19</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>77</v>
@@ -14443,7 +14452,7 @@
         <v>19</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>19</v>
@@ -14451,14 +14460,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14480,16 +14489,16 @@
         <v>134</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>19</v>
@@ -14538,7 +14547,7 @@
         <v>19</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>77</v>
@@ -14567,14 +14576,14 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -14593,13 +14602,13 @@
         <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14626,11 +14635,11 @@
         <v>19</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>19</v>
@@ -14648,7 +14657,7 @@
         <v>19</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>77</v>
@@ -14663,24 +14672,24 @@
         <v>99</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14703,13 +14712,13 @@
         <v>19</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14739,10 +14748,10 @@
         <v>111</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>19</v>
@@ -14760,7 +14769,7 @@
         <v>19</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>77</v>
@@ -14781,18 +14790,18 @@
         <v>19</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14815,16 +14824,16 @@
         <v>19</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14874,7 +14883,7 @@
         <v>19</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>77</v>
@@ -14895,7 +14904,7 @@
         <v>19</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>19</v>
@@ -14903,10 +14912,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14929,19 +14938,19 @@
         <v>19</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>19</v>
@@ -14966,13 +14975,13 @@
         <v>19</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>19</v>
@@ -14990,7 +14999,7 @@
         <v>19</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>77</v>
@@ -15011,18 +15020,18 @@
         <v>19</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15045,13 +15054,13 @@
         <v>19</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15078,13 +15087,13 @@
         <v>19</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>19</v>
@@ -15102,7 +15111,7 @@
         <v>19</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
@@ -15123,18 +15132,18 @@
         <v>19</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15157,16 +15166,16 @@
         <v>19</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -15192,13 +15201,13 @@
         <v>19</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>19</v>
@@ -15216,7 +15225,7 @@
         <v>19</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>77</v>
@@ -15237,18 +15246,18 @@
         <v>19</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15271,16 +15280,16 @@
         <v>19</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -15330,7 +15339,7 @@
         <v>19</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>77</v>
@@ -15351,7 +15360,7 @@
         <v>19</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>19</v>
@@ -15359,10 +15368,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15385,13 +15394,13 @@
         <v>19</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15442,7 +15451,7 @@
         <v>19</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>77</v>
@@ -15451,7 +15460,7 @@
         <v>87</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>19</v>
@@ -15463,7 +15472,7 @@
         <v>19</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>19</v>
@@ -15471,10 +15480,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15552,7 +15561,7 @@
         <v>138</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>77</v>
@@ -15581,13 +15590,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="B116" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="B116" t="s" s="2">
-        <v>615</v>
-      </c>
       <c r="C116" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>19</v>
@@ -15609,13 +15618,13 @@
         <v>19</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15666,7 +15675,7 @@
         <v>19</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>77</v>
@@ -15695,13 +15704,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>19</v>
@@ -15723,13 +15732,13 @@
         <v>19</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -15780,7 +15789,7 @@
         <v>19</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>77</v>
@@ -15809,14 +15818,14 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -15838,16 +15847,16 @@
         <v>134</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>19</v>
@@ -15896,7 +15905,7 @@
         <v>19</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>77</v>
@@ -15925,10 +15934,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15951,13 +15960,13 @@
         <v>19</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16008,7 +16017,7 @@
         <v>19</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>77</v>
@@ -16029,18 +16038,18 @@
         <v>19</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16063,13 +16072,13 @@
         <v>19</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16120,7 +16129,7 @@
         <v>19</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>77</v>
@@ -16141,7 +16150,7 @@
         <v>19</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>19</v>
@@ -16149,10 +16158,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16175,13 +16184,13 @@
         <v>19</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16208,31 +16217,31 @@
         <v>19</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Y121" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF121" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>633</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>77</v>
@@ -16253,18 +16262,18 @@
         <v>19</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16287,13 +16296,13 @@
         <v>19</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16320,31 +16329,31 @@
         <v>19</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Y122" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF122" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>77</v>
@@ -16365,18 +16374,18 @@
         <v>19</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16399,13 +16408,13 @@
         <v>19</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16456,7 +16465,7 @@
         <v>19</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>77</v>
@@ -16477,18 +16486,18 @@
         <v>19</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16511,13 +16520,13 @@
         <v>19</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16548,25 +16557,25 @@
       </c>
       <c r="Y124" s="2"/>
       <c r="Z124" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF124" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>651</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>77</v>
@@ -16587,18 +16596,18 @@
         <v>19</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16621,16 +16630,16 @@
         <v>19</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -16680,7 +16689,7 @@
         <v>19</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>77</v>
@@ -16701,7 +16710,7 @@
         <v>19</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>19</v>
@@ -16709,10 +16718,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16735,13 +16744,13 @@
         <v>19</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16792,7 +16801,7 @@
         <v>19</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>77</v>
@@ -16801,7 +16810,7 @@
         <v>87</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>19</v>
@@ -16813,7 +16822,7 @@
         <v>19</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>19</v>
@@ -16821,14 +16830,14 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
@@ -16850,13 +16859,13 @@
         <v>134</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -16906,7 +16915,7 @@
         <v>19</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>77</v>
@@ -16927,7 +16936,7 @@
         <v>19</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>19</v>
@@ -16935,14 +16944,14 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -16964,16 +16973,16 @@
         <v>134</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>19</v>
@@ -17022,7 +17031,7 @@
         <v>19</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>77</v>
@@ -17051,10 +17060,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17077,13 +17086,13 @@
         <v>19</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17134,7 +17143,7 @@
         <v>19</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>87</v>
@@ -17149,24 +17158,24 @@
         <v>99</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17192,13 +17201,13 @@
         <v>107</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -17227,10 +17236,10 @@
         <v>111</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>19</v>
@@ -17248,7 +17257,7 @@
         <v>19</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>77</v>
@@ -17269,7 +17278,7 @@
         <v>19</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>19</v>
@@ -17277,10 +17286,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17303,16 +17312,16 @@
         <v>19</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -17338,13 +17347,13 @@
         <v>19</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>19</v>
@@ -17362,7 +17371,7 @@
         <v>19</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>77</v>
@@ -17391,10 +17400,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17417,13 +17426,13 @@
         <v>19</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -17474,7 +17483,7 @@
         <v>19</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>77</v>
@@ -17495,7 +17504,7 @@
         <v>19</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>19</v>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T10:21:23+00:00</t>
+    <t>2024-10-29T14:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1829,7 +1829,7 @@
     <t>Code für den Typ der LKF Diagnose, der angibt ob es sich um eine Haupt- oder Nebendiagnose handelt</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet/lkf-diagnose-typ</t>
+    <t>https://termgit.elga.gv.at/ValueSet-lkf-diagnose-typ.html</t>
   </si>
   <si>
     <t>DG1-6 (Diagnosis Type)</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T14:54:01+00:00</t>
+    <t>2024-10-31T07:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T07:20:54+00:00</t>
+    <t>2024-11-06T10:03:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:03:56+00:00</t>
+    <t>2024-11-06T10:30:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:30:49+00:00</t>
+    <t>2024-11-06T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T13:09:39+00:00</t>
+    <t>2024-11-06T14:31:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-11T09:21:50+00:00</t>
+    <t>2024-11-11T13:58:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>87</v>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:47:57+00:00</t>
+    <t>2024-11-12T08:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4758" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5554" uniqueCount="726">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:54:48+00:00</t>
+    <t>2024-11-12T10:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1110,6 +1110,75 @@
     <t>http://example.org/ValueSet/moped-behandlungsart-valueset</t>
   </si>
   <si>
+    <t>Encounter.class:Behandlungsart.id</t>
+  </si>
+  <si>
+    <t>Encounter.class.id</t>
+  </si>
+  <si>
+    <t>Encounter.class:Behandlungsart.extension</t>
+  </si>
+  <si>
+    <t>Encounter.class.extension</t>
+  </si>
+  <si>
+    <t>Encounter.class:Behandlungsart.coding</t>
+  </si>
+  <si>
+    <t>Encounter.class.coding</t>
+  </si>
+  <si>
+    <t>Encounter.class:Behandlungsart.coding.id</t>
+  </si>
+  <si>
+    <t>Encounter.class.coding.id</t>
+  </si>
+  <si>
+    <t>Encounter.class:Behandlungsart.coding.extension</t>
+  </si>
+  <si>
+    <t>Encounter.class.coding.extension</t>
+  </si>
+  <si>
+    <t>Encounter.class:Behandlungsart.coding.system</t>
+  </si>
+  <si>
+    <t>Encounter.class.coding.system</t>
+  </si>
+  <si>
+    <t>http://tbd.at/MOPED-encounter-behandlungsart</t>
+  </si>
+  <si>
+    <t>Encounter.class:Behandlungsart.coding.version</t>
+  </si>
+  <si>
+    <t>Encounter.class.coding.version</t>
+  </si>
+  <si>
+    <t>Encounter.class:Behandlungsart.coding.code</t>
+  </si>
+  <si>
+    <t>Encounter.class.coding.code</t>
+  </si>
+  <si>
+    <t>Encounter.class:Behandlungsart.coding.display</t>
+  </si>
+  <si>
+    <t>Encounter.class.coding.display</t>
+  </si>
+  <si>
+    <t>Encounter.class:Behandlungsart.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Encounter.class.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Encounter.class:Behandlungsart.text</t>
+  </si>
+  <si>
+    <t>Encounter.class.text</t>
+  </si>
+  <si>
     <t>Encounter.class:Aufnahmeart</t>
   </si>
   <si>
@@ -1117,6 +1186,42 @@
   </si>
   <si>
     <t>http://example.org/ValueSet/moped-aufnahmeart-valueset</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.id</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.extension</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.coding</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.coding.id</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.coding.extension</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.coding.system</t>
+  </si>
+  <si>
+    <t>http://tbd.at/moped-ext-aufnahmeart</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.coding.version</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.coding.code</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.coding.display</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart.text</t>
   </si>
   <si>
     <t>Encounter.priority</t>
@@ -2478,7 +2583,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN132"/>
+  <dimension ref="A1:AN154"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.9453125" customWidth="true" bestFit="true"/>
@@ -8797,11 +8902,9 @@
         <v>354</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="C56" t="s" s="2">
         <v>355</v>
       </c>
+      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>19</v>
       </c>
@@ -8819,16 +8922,16 @@
         <v>19</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>189</v>
+        <v>89</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>355</v>
+        <v>166</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>343</v>
+        <v>167</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8855,11 +8958,13 @@
         <v>19</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="Y56" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z56" t="s" s="2">
-        <v>356</v>
+        <v>19</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>19</v>
@@ -8877,50 +8982,50 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>341</v>
+        <v>168</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>348</v>
+        <v>19</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>349</v>
+        <v>170</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>350</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>357</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>19</v>
+        <v>147</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>19</v>
@@ -8932,15 +9037,17 @@
         <v>19</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>189</v>
+        <v>134</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>358</v>
+        <v>173</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>19</v>
@@ -8965,63 +9072,63 @@
         <v>19</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>359</v>
+        <v>19</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>361</v>
+        <v>19</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>19</v>
+        <v>175</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>357</v>
+        <v>176</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>362</v>
+        <v>19</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>363</v>
+        <v>170</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>364</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9044,18 +9151,20 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>366</v>
+        <v>204</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>367</v>
+        <v>205</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>206</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>19</v>
       </c>
@@ -9079,13 +9188,13 @@
         <v>19</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>369</v>
+        <v>19</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>370</v>
+        <v>19</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>19</v>
@@ -9103,7 +9212,7 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>365</v>
+        <v>208</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -9118,24 +9227,24 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>371</v>
+        <v>19</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>372</v>
+        <v>19</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>373</v>
+        <v>209</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>374</v>
+        <v>210</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9146,7 +9255,7 @@
         <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>19</v>
@@ -9155,16 +9264,16 @@
         <v>19</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>376</v>
+        <v>89</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>377</v>
+        <v>166</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>378</v>
+        <v>167</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9191,13 +9300,13 @@
         <v>19</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>379</v>
+        <v>19</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>380</v>
+        <v>19</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>19</v>
@@ -9215,22 +9324,22 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>375</v>
+        <v>168</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>371</v>
+        <v>19</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>19</v>
@@ -9239,26 +9348,26 @@
         <v>170</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>381</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>383</v>
+        <v>147</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>19</v>
@@ -9267,19 +9376,19 @@
         <v>19</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>384</v>
+        <v>134</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>385</v>
+        <v>173</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>386</v>
+        <v>174</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>387</v>
+        <v>150</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9317,51 +9426,51 @@
         <v>19</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>19</v>
+        <v>175</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>382</v>
+        <v>176</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>388</v>
+        <v>19</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>389</v>
+        <v>19</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>390</v>
+        <v>170</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>391</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>392</v>
+        <v>365</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9369,7 +9478,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>87</v>
@@ -9381,21 +9490,23 @@
         <v>19</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>189</v>
+        <v>101</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>393</v>
+        <v>217</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>394</v>
+        <v>218</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>19</v>
       </c>
@@ -9404,7 +9515,7 @@
         <v>19</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>19</v>
+        <v>366</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>19</v>
@@ -9419,13 +9530,13 @@
         <v>19</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>396</v>
+        <v>19</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>397</v>
+        <v>19</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>19</v>
@@ -9443,7 +9554,7 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>392</v>
+        <v>221</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -9464,18 +9575,18 @@
         <v>19</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>19</v>
+        <v>222</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>19</v>
+        <v>223</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>398</v>
+        <v>367</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>398</v>
+        <v>368</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9486,7 +9597,7 @@
         <v>77</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>19</v>
@@ -9498,15 +9609,17 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>399</v>
+        <v>226</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>400</v>
+        <v>227</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>19</v>
@@ -9555,13 +9668,13 @@
         <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>398</v>
+        <v>230</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>19</v>
@@ -9573,32 +9686,32 @@
         <v>19</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>402</v>
+        <v>19</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>170</v>
+        <v>231</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>403</v>
+        <v>232</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>404</v>
+        <v>369</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>404</v>
+        <v>370</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>405</v>
+        <v>19</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>19</v>
@@ -9607,19 +9720,21 @@
         <v>19</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>406</v>
+        <v>107</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>407</v>
+        <v>235</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>408</v>
+        <v>236</v>
       </c>
       <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>19</v>
       </c>
@@ -9667,39 +9782,39 @@
         <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>404</v>
+        <v>239</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>19</v>
+        <v>240</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>409</v>
+        <v>19</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>410</v>
+        <v>241</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>19</v>
+        <v>242</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>411</v>
+        <v>371</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>411</v>
+        <v>372</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9710,7 +9825,7 @@
         <v>77</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>19</v>
@@ -9719,19 +9834,21 @@
         <v>19</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>412</v>
+        <v>226</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>413</v>
+        <v>245</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>414</v>
+        <v>246</v>
       </c>
       <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>19</v>
       </c>
@@ -9779,16 +9896,16 @@
         <v>19</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>411</v>
+        <v>248</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>19</v>
+        <v>240</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>99</v>
@@ -9800,18 +9917,18 @@
         <v>19</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>170</v>
+        <v>249</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>19</v>
+        <v>250</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>415</v>
+        <v>373</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>415</v>
+        <v>374</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9831,21 +9948,23 @@
         <v>19</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>416</v>
+        <v>253</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>417</v>
+        <v>254</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>418</v>
+        <v>255</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="O65" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>19</v>
       </c>
@@ -9893,7 +10012,7 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>415</v>
+        <v>258</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9908,24 +10027,24 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>420</v>
+        <v>19</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>421</v>
+        <v>259</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>19</v>
+        <v>260</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>422</v>
+        <v>375</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>422</v>
+        <v>376</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9945,19 +10064,23 @@
         <v>19</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>423</v>
+        <v>226</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>424</v>
+        <v>263</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>19</v>
       </c>
@@ -10005,7 +10128,7 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>422</v>
+        <v>267</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -10020,26 +10143,28 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>426</v>
+        <v>19</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>427</v>
+        <v>268</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>428</v>
+        <v>269</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>429</v>
+        <v>377</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="C67" s="2"/>
+        <v>341</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="D67" t="s" s="2">
         <v>19</v>
       </c>
@@ -10048,7 +10173,7 @@
         <v>77</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>19</v>
@@ -10060,17 +10185,15 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>430</v>
+        <v>189</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>431</v>
+        <v>378</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>19</v>
@@ -10095,13 +10218,11 @@
         <v>19</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>19</v>
+        <v>379</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>19</v>
@@ -10119,7 +10240,7 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>429</v>
+        <v>341</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -10131,27 +10252,27 @@
         <v>19</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>434</v>
+        <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>435</v>
+        <v>19</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>19</v>
+        <v>348</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>436</v>
+        <v>349</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>437</v>
+        <v>350</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>438</v>
+        <v>380</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>438</v>
+        <v>355</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10174,7 +10295,7 @@
         <v>19</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>226</v>
+        <v>89</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>166</v>
@@ -10260,10 +10381,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>439</v>
+        <v>381</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>439</v>
+        <v>357</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10333,16 +10454,16 @@
         <v>19</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>19</v>
+        <v>175</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>176</v>
@@ -10374,14 +10495,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>440</v>
+        <v>382</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>440</v>
+        <v>359</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10394,25 +10515,25 @@
         <v>19</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J70" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>134</v>
+        <v>203</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>442</v>
+        <v>204</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>443</v>
+        <v>205</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>150</v>
+        <v>206</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>151</v>
+        <v>207</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>19</v>
@@ -10461,7 +10582,7 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>444</v>
+        <v>208</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -10473,7 +10594,7 @@
         <v>19</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>19</v>
@@ -10482,18 +10603,18 @@
         <v>19</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>132</v>
+        <v>209</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>19</v>
+        <v>210</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>445</v>
+        <v>383</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>445</v>
+        <v>361</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10504,7 +10625,7 @@
         <v>77</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>19</v>
@@ -10513,20 +10634,18 @@
         <v>19</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>189</v>
+        <v>89</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>446</v>
+        <v>166</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>448</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>19</v>
@@ -10551,13 +10670,13 @@
         <v>19</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>449</v>
+        <v>19</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>447</v>
+        <v>19</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>450</v>
+        <v>19</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>19</v>
@@ -10575,50 +10694,50 @@
         <v>19</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>445</v>
+        <v>168</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>451</v>
+        <v>169</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>452</v>
+        <v>19</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>453</v>
+        <v>170</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>454</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>455</v>
+        <v>384</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>455</v>
+        <v>363</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>19</v>
+        <v>147</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>19</v>
@@ -10630,15 +10749,17 @@
         <v>19</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>292</v>
+        <v>134</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>456</v>
+        <v>173</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>19</v>
@@ -10675,31 +10796,31 @@
         <v>19</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>19</v>
+        <v>175</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>455</v>
+        <v>176</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>19</v>
@@ -10708,18 +10829,18 @@
         <v>19</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>458</v>
+        <v>170</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>459</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>460</v>
+        <v>385</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>460</v>
+        <v>365</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10727,7 +10848,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>87</v>
@@ -10742,18 +10863,20 @@
         <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>461</v>
+        <v>101</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>462</v>
+        <v>217</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>463</v>
+        <v>218</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>19</v>
       </c>
@@ -10762,7 +10885,7 @@
         <v>19</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>19</v>
+        <v>386</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>19</v>
@@ -10801,7 +10924,7 @@
         <v>19</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>460</v>
+        <v>221</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -10810,30 +10933,30 @@
         <v>87</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>451</v>
+        <v>19</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>426</v>
+        <v>19</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>465</v>
+        <v>19</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>466</v>
+        <v>222</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>467</v>
+        <v>223</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>468</v>
+        <v>387</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>468</v>
+        <v>368</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10844,7 +10967,7 @@
         <v>77</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>19</v>
@@ -10856,15 +10979,17 @@
         <v>88</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>469</v>
+        <v>226</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>470</v>
+        <v>227</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>19</v>
@@ -10913,13 +11038,13 @@
         <v>19</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>468</v>
+        <v>230</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>19</v>
@@ -10928,24 +11053,24 @@
         <v>99</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>409</v>
+        <v>19</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>472</v>
+        <v>231</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>473</v>
+        <v>232</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>474</v>
+        <v>388</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>474</v>
+        <v>370</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10956,7 +11081,7 @@
         <v>77</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>19</v>
@@ -10965,21 +11090,21 @@
         <v>19</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>475</v>
+        <v>107</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>476</v>
+        <v>235</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>19</v>
       </c>
@@ -11027,16 +11152,16 @@
         <v>19</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>474</v>
+        <v>239</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>19</v>
+        <v>240</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>99</v>
@@ -11048,18 +11173,18 @@
         <v>19</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>132</v>
+        <v>241</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>19</v>
+        <v>242</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>479</v>
+        <v>389</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>479</v>
+        <v>372</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11079,21 +11204,21 @@
         <v>19</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>292</v>
+        <v>226</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>480</v>
+        <v>245</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>19</v>
       </c>
@@ -11141,7 +11266,7 @@
         <v>19</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>479</v>
+        <v>248</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
@@ -11150,30 +11275,30 @@
         <v>87</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>19</v>
+        <v>240</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>483</v>
+        <v>19</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>484</v>
+        <v>19</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>485</v>
+        <v>249</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>486</v>
+        <v>250</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>487</v>
+        <v>390</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>487</v>
+        <v>374</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11193,19 +11318,23 @@
         <v>19</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>488</v>
+        <v>253</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>489</v>
+        <v>254</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>19</v>
       </c>
@@ -11253,7 +11382,7 @@
         <v>19</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>487</v>
+        <v>258</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -11274,18 +11403,18 @@
         <v>19</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>19</v>
+        <v>259</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>491</v>
+        <v>260</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>492</v>
+        <v>391</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>492</v>
+        <v>376</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11305,19 +11434,23 @@
         <v>19</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>488</v>
+        <v>226</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>493</v>
+        <v>263</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>19</v>
       </c>
@@ -11365,7 +11498,7 @@
         <v>19</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>492</v>
+        <v>267</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -11386,18 +11519,18 @@
         <v>19</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>19</v>
+        <v>268</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>495</v>
+        <v>269</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>496</v>
+        <v>392</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>496</v>
+        <v>392</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11420,17 +11553,15 @@
         <v>19</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>497</v>
+        <v>189</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>498</v>
+        <v>393</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>500</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>19</v>
@@ -11455,13 +11586,13 @@
         <v>19</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>19</v>
+        <v>395</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>19</v>
+        <v>394</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>19</v>
+        <v>396</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>19</v>
@@ -11479,7 +11610,7 @@
         <v>19</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>496</v>
+        <v>392</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
@@ -11494,24 +11625,24 @@
         <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>483</v>
+        <v>19</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>19</v>
+        <v>397</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>501</v>
+        <v>398</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>502</v>
+        <v>399</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>503</v>
+        <v>400</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>503</v>
+        <v>400</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11534,16 +11665,16 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>430</v>
+        <v>189</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>504</v>
+        <v>401</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>505</v>
+        <v>402</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>506</v>
+        <v>403</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11569,29 +11700,31 @@
         <v>19</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>19</v>
+        <v>395</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>19</v>
+        <v>404</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>19</v>
+        <v>405</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AC80" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD80" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>503</v>
+        <v>400</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -11606,24 +11739,24 @@
         <v>99</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>19</v>
+        <v>406</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>19</v>
+        <v>407</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>19</v>
+        <v>408</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>19</v>
+        <v>409</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>508</v>
+        <v>410</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>508</v>
+        <v>410</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11634,7 +11767,7 @@
         <v>77</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>19</v>
@@ -11643,16 +11776,16 @@
         <v>19</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>226</v>
+        <v>411</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>166</v>
+        <v>412</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>167</v>
+        <v>413</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11679,13 +11812,13 @@
         <v>19</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>19</v>
+        <v>395</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>19</v>
+        <v>414</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>19</v>
+        <v>415</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>19</v>
@@ -11703,22 +11836,22 @@
         <v>19</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>168</v>
+        <v>410</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>169</v>
+        <v>19</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>19</v>
+        <v>406</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>19</v>
@@ -11727,26 +11860,26 @@
         <v>170</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>19</v>
+        <v>416</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>509</v>
+        <v>417</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>509</v>
+        <v>417</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>147</v>
+        <v>418</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>19</v>
@@ -11755,19 +11888,19 @@
         <v>19</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>134</v>
+        <v>419</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>173</v>
+        <v>420</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>174</v>
+        <v>421</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>150</v>
+        <v>422</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11817,75 +11950,73 @@
         <v>19</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>176</v>
+        <v>417</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>19</v>
+        <v>423</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>19</v>
+        <v>424</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>170</v>
+        <v>425</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>19</v>
+        <v>426</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>510</v>
+        <v>427</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>510</v>
+        <v>427</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I83" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>134</v>
+        <v>189</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>19</v>
       </c>
@@ -11909,13 +12040,13 @@
         <v>19</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>19</v>
+        <v>395</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>19</v>
+        <v>431</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>19</v>
+        <v>432</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>19</v>
@@ -11933,19 +12064,19 @@
         <v>19</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>444</v>
+        <v>427</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>19</v>
@@ -11954,7 +12085,7 @@
         <v>19</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>19</v>
@@ -11962,10 +12093,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>511</v>
+        <v>433</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>511</v>
+        <v>433</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11988,13 +12119,13 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>189</v>
+        <v>434</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>512</v>
+        <v>435</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>513</v>
+        <v>436</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12021,11 +12152,13 @@
         <v>19</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="Y84" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z84" t="s" s="2">
-        <v>514</v>
+        <v>19</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>19</v>
@@ -12043,7 +12176,7 @@
         <v>19</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>511</v>
+        <v>433</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
@@ -12061,25 +12194,25 @@
         <v>19</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>19</v>
+        <v>437</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>19</v>
+        <v>438</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>515</v>
+        <v>439</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>515</v>
+        <v>439</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>516</v>
+        <v>440</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12095,16 +12228,16 @@
         <v>19</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>517</v>
+        <v>441</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>518</v>
+        <v>442</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>519</v>
+        <v>443</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12131,13 +12264,13 @@
         <v>19</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>344</v>
+        <v>19</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>520</v>
+        <v>19</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>521</v>
+        <v>19</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>19</v>
@@ -12155,7 +12288,7 @@
         <v>19</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>515</v>
+        <v>439</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
@@ -12170,28 +12303,26 @@
         <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>522</v>
+        <v>444</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>523</v>
+        <v>19</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>524</v>
+        <v>445</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>525</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>526</v>
+        <v>446</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>527</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>19</v>
       </c>
@@ -12200,7 +12331,7 @@
         <v>77</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>19</v>
@@ -12209,20 +12340,18 @@
         <v>19</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>528</v>
+        <v>448</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>506</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>19</v>
@@ -12271,7 +12400,7 @@
         <v>19</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>503</v>
+        <v>446</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>77</v>
@@ -12292,7 +12421,7 @@
         <v>19</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>19</v>
@@ -12300,10 +12429,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>529</v>
+        <v>450</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>508</v>
+        <v>450</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12326,15 +12455,17 @@
         <v>19</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>226</v>
+        <v>451</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>166</v>
+        <v>452</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>19</v>
@@ -12383,7 +12514,7 @@
         <v>19</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>168</v>
+        <v>450</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>77</v>
@@ -12392,19 +12523,19 @@
         <v>87</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>169</v>
+        <v>19</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>19</v>
+        <v>455</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>170</v>
+        <v>456</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>19</v>
@@ -12412,21 +12543,21 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>530</v>
+        <v>457</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>509</v>
+        <v>457</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>19</v>
@@ -12438,17 +12569,15 @@
         <v>19</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>134</v>
+        <v>458</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>173</v>
+        <v>459</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>19</v>
@@ -12497,43 +12626,43 @@
         <v>19</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>176</v>
+        <v>457</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>19</v>
+        <v>461</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>170</v>
+        <v>462</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>19</v>
+        <v>463</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>531</v>
+        <v>464</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>510</v>
+        <v>464</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12546,26 +12675,24 @@
         <v>19</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J89" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>134</v>
+        <v>465</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>19</v>
       </c>
@@ -12613,7 +12740,7 @@
         <v>19</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>444</v>
+        <v>464</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -12625,27 +12752,27 @@
         <v>19</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>140</v>
+        <v>469</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>19</v>
+        <v>470</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>132</v>
+        <v>471</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>19</v>
+        <v>472</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>532</v>
+        <v>473</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>511</v>
+        <v>473</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12656,7 +12783,7 @@
         <v>77</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>19</v>
@@ -12665,16 +12792,16 @@
         <v>19</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>512</v>
+        <v>166</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>513</v>
+        <v>167</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12701,11 +12828,13 @@
         <v>19</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="Y90" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z90" t="s" s="2">
-        <v>514</v>
+        <v>19</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>19</v>
@@ -12723,19 +12852,19 @@
         <v>19</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>511</v>
+        <v>168</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>19</v>
@@ -12744,7 +12873,7 @@
         <v>19</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>19</v>
@@ -12752,21 +12881,21 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>533</v>
+        <v>474</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>534</v>
+        <v>474</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>19</v>
+        <v>147</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>19</v>
@@ -12778,15 +12907,17 @@
         <v>19</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>19</v>
@@ -12835,19 +12966,19 @@
         <v>19</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>169</v>
+        <v>19</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>19</v>
@@ -12864,14 +12995,14 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>535</v>
+        <v>475</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>536</v>
+        <v>475</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>147</v>
+        <v>476</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -12884,24 +13015,26 @@
         <v>19</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K92" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>173</v>
+        <v>477</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>174</v>
+        <v>478</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="O92" s="2"/>
+      <c r="O92" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>19</v>
       </c>
@@ -12937,19 +13070,19 @@
         <v>19</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>175</v>
+        <v>19</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>176</v>
+        <v>479</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>77</v>
@@ -12970,7 +13103,7 @@
         <v>19</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>170</v>
+        <v>132</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>19</v>
@@ -12978,10 +13111,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>537</v>
+        <v>480</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>538</v>
+        <v>480</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13004,20 +13137,18 @@
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>204</v>
+        <v>481</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>205</v>
+        <v>482</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>207</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>19</v>
       </c>
@@ -13041,13 +13172,13 @@
         <v>19</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>19</v>
+        <v>484</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>19</v>
+        <v>482</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>19</v>
+        <v>485</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>19</v>
@@ -13065,7 +13196,7 @@
         <v>19</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>208</v>
+        <v>480</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>77</v>
@@ -13074,30 +13205,30 @@
         <v>78</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>19</v>
+        <v>486</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>19</v>
+        <v>487</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>209</v>
+        <v>488</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>210</v>
+        <v>489</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>539</v>
+        <v>490</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>540</v>
+        <v>490</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13120,13 +13251,13 @@
         <v>19</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>89</v>
+        <v>292</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>166</v>
+        <v>491</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>167</v>
+        <v>492</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13177,7 +13308,7 @@
         <v>19</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>168</v>
+        <v>490</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>77</v>
@@ -13186,10 +13317,10 @@
         <v>87</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>169</v>
+        <v>19</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>19</v>
@@ -13198,29 +13329,29 @@
         <v>19</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>170</v>
+        <v>493</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>19</v>
+        <v>494</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>541</v>
+        <v>495</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>542</v>
+        <v>495</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>19</v>
@@ -13229,19 +13360,19 @@
         <v>19</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>134</v>
+        <v>496</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>173</v>
+        <v>497</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>174</v>
+        <v>498</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>150</v>
+        <v>499</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13279,51 +13410,51 @@
         <v>19</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>175</v>
+        <v>19</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>176</v>
+        <v>495</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>19</v>
+        <v>486</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>19</v>
+        <v>461</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>19</v>
+        <v>500</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>170</v>
+        <v>501</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>19</v>
+        <v>502</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>543</v>
+        <v>503</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>544</v>
+        <v>503</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13334,7 +13465,7 @@
         <v>77</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>19</v>
@@ -13346,20 +13477,16 @@
         <v>88</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>101</v>
+        <v>504</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>217</v>
+        <v>505</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>506</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>19</v>
       </c>
@@ -13407,13 +13534,13 @@
         <v>19</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>221</v>
+        <v>503</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>19</v>
@@ -13422,24 +13549,24 @@
         <v>99</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>19</v>
+        <v>444</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>222</v>
+        <v>507</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>223</v>
+        <v>508</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>545</v>
+        <v>509</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>546</v>
+        <v>509</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13450,7 +13577,7 @@
         <v>77</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>19</v>
@@ -13459,19 +13586,19 @@
         <v>19</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>226</v>
+        <v>510</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>227</v>
+        <v>511</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>228</v>
+        <v>512</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>229</v>
+        <v>513</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13521,13 +13648,13 @@
         <v>19</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>230</v>
+        <v>509</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>19</v>
@@ -13542,18 +13669,18 @@
         <v>19</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>231</v>
+        <v>132</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>232</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>547</v>
+        <v>514</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>548</v>
+        <v>514</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13561,7 +13688,7 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>87</v>
@@ -13573,27 +13700,27 @@
         <v>19</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>107</v>
+        <v>292</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>235</v>
+        <v>515</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" t="s" s="2">
-        <v>237</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>19</v>
       </c>
       <c r="Q98" s="2"/>
       <c r="R98" t="s" s="2">
-        <v>549</v>
+        <v>19</v>
       </c>
       <c r="S98" t="s" s="2">
         <v>19</v>
@@ -13635,7 +13762,7 @@
         <v>19</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>239</v>
+        <v>514</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>77</v>
@@ -13644,30 +13771,30 @@
         <v>87</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>240</v>
+        <v>19</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>19</v>
+        <v>518</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>19</v>
+        <v>519</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>241</v>
+        <v>520</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>242</v>
+        <v>521</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>550</v>
+        <v>522</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>551</v>
+        <v>522</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13687,21 +13814,19 @@
         <v>19</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>226</v>
+        <v>523</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>245</v>
+        <v>524</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>246</v>
+        <v>525</v>
       </c>
       <c r="N99" s="2"/>
-      <c r="O99" t="s" s="2">
-        <v>247</v>
-      </c>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>19</v>
       </c>
@@ -13749,7 +13874,7 @@
         <v>19</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>248</v>
+        <v>522</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>77</v>
@@ -13758,7 +13883,7 @@
         <v>87</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>240</v>
+        <v>19</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>99</v>
@@ -13770,18 +13895,18 @@
         <v>19</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>249</v>
+        <v>19</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>250</v>
+        <v>526</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>552</v>
+        <v>527</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>553</v>
+        <v>527</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13801,23 +13926,19 @@
         <v>19</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>253</v>
+        <v>523</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>254</v>
+        <v>528</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>19</v>
       </c>
@@ -13865,7 +13986,7 @@
         <v>19</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>258</v>
+        <v>527</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>77</v>
@@ -13886,18 +14007,18 @@
         <v>19</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>259</v>
+        <v>19</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>260</v>
+        <v>530</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>554</v>
+        <v>531</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>555</v>
+        <v>531</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13917,23 +14038,21 @@
         <v>19</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>226</v>
+        <v>532</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>263</v>
+        <v>533</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>264</v>
+        <v>534</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>19</v>
       </c>
@@ -13981,7 +14100,7 @@
         <v>19</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>267</v>
+        <v>531</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>77</v>
@@ -13996,28 +14115,28 @@
         <v>99</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>19</v>
+        <v>518</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>268</v>
+        <v>536</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>269</v>
+        <v>537</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>556</v>
+        <v>538</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>515</v>
+        <v>538</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>516</v>
+        <v>19</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14036,15 +14155,17 @@
         <v>88</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>517</v>
+        <v>465</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>518</v>
+        <v>539</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>540</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>541</v>
+      </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>19</v>
@@ -14069,29 +14190,29 @@
         <v>19</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="Y102" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z102" t="s" s="2">
-        <v>557</v>
+        <v>19</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="AC102" s="2"/>
       <c r="AD102" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>515</v>
+        <v>538</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
@@ -14106,24 +14227,24 @@
         <v>99</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>522</v>
+        <v>19</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>523</v>
+        <v>19</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>524</v>
+        <v>19</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>525</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>558</v>
+        <v>543</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>558</v>
+        <v>543</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14134,7 +14255,7 @@
         <v>77</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>19</v>
@@ -14143,20 +14264,18 @@
         <v>19</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>430</v>
+        <v>226</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>559</v>
+        <v>166</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>561</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>19</v>
@@ -14205,19 +14324,19 @@
         <v>19</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>558</v>
+        <v>168</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>19</v>
@@ -14226,7 +14345,7 @@
         <v>19</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>562</v>
+        <v>170</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>19</v>
@@ -14234,21 +14353,21 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>563</v>
+        <v>544</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>563</v>
+        <v>544</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>19</v>
+        <v>147</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>19</v>
@@ -14260,15 +14379,17 @@
         <v>19</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>226</v>
+        <v>134</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>19</v>
@@ -14317,19 +14438,19 @@
         <v>19</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>169</v>
+        <v>19</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>19</v>
@@ -14346,14 +14467,14 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>564</v>
+        <v>545</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>564</v>
+        <v>545</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>147</v>
+        <v>476</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -14366,24 +14487,26 @@
         <v>19</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K105" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>173</v>
+        <v>477</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>174</v>
+        <v>478</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="O105" s="2"/>
+      <c r="O105" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>19</v>
       </c>
@@ -14431,7 +14554,7 @@
         <v>19</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>176</v>
+        <v>479</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>77</v>
@@ -14452,7 +14575,7 @@
         <v>19</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>170</v>
+        <v>132</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>19</v>
@@ -14460,14 +14583,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>565</v>
+        <v>546</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>565</v>
+        <v>546</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14480,26 +14603,22 @@
         <v>19</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J106" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>134</v>
+        <v>189</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>442</v>
+        <v>547</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>19</v>
       </c>
@@ -14523,13 +14642,11 @@
         <v>19</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="Y106" s="2"/>
       <c r="Z106" t="s" s="2">
-        <v>19</v>
+        <v>549</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>19</v>
@@ -14547,7 +14664,7 @@
         <v>19</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>444</v>
+        <v>546</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>77</v>
@@ -14559,7 +14676,7 @@
         <v>19</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>19</v>
@@ -14568,7 +14685,7 @@
         <v>19</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>19</v>
@@ -14576,14 +14693,14 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>566</v>
+        <v>550</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>566</v>
+        <v>550</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -14602,13 +14719,13 @@
         <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>568</v>
+        <v>552</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>569</v>
+        <v>553</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>570</v>
+        <v>554</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14635,11 +14752,13 @@
         <v>19</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="Y107" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>555</v>
+      </c>
       <c r="Z107" t="s" s="2">
-        <v>571</v>
+        <v>556</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>19</v>
@@ -14657,7 +14776,7 @@
         <v>19</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>566</v>
+        <v>550</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>77</v>
@@ -14672,26 +14791,28 @@
         <v>99</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>522</v>
+        <v>557</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>523</v>
+        <v>558</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>573</v>
+        <v>560</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="C108" s="2"/>
+        <v>538</v>
+      </c>
+      <c r="C108" t="s" s="2">
+        <v>562</v>
+      </c>
       <c r="D108" t="s" s="2">
         <v>19</v>
       </c>
@@ -14700,7 +14821,7 @@
         <v>77</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>19</v>
@@ -14709,18 +14830,20 @@
         <v>19</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>189</v>
+        <v>465</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>540</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>541</v>
+      </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>19</v>
@@ -14745,13 +14868,13 @@
         <v>19</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>577</v>
+        <v>19</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>578</v>
+        <v>19</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>19</v>
@@ -14769,7 +14892,7 @@
         <v>19</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>574</v>
+        <v>538</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>77</v>
@@ -14790,18 +14913,18 @@
         <v>19</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>170</v>
+        <v>19</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>579</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>580</v>
+        <v>543</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14812,7 +14935,7 @@
         <v>77</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>19</v>
@@ -14824,17 +14947,15 @@
         <v>19</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>581</v>
+        <v>226</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>582</v>
+        <v>166</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>584</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>19</v>
@@ -14883,19 +15004,19 @@
         <v>19</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>580</v>
+        <v>168</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>19</v>
@@ -14904,7 +15025,7 @@
         <v>19</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>585</v>
+        <v>170</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>19</v>
@@ -14912,14 +15033,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>586</v>
+        <v>565</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>586</v>
+        <v>544</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>19</v>
+        <v>147</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -14938,20 +15059,18 @@
         <v>19</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>189</v>
+        <v>134</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>587</v>
+        <v>173</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>588</v>
+        <v>174</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>590</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>19</v>
       </c>
@@ -14975,13 +15094,13 @@
         <v>19</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>591</v>
+        <v>19</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>592</v>
+        <v>19</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>19</v>
@@ -14999,7 +15118,7 @@
         <v>19</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>586</v>
+        <v>176</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>77</v>
@@ -15011,7 +15130,7 @@
         <v>19</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>19</v>
@@ -15020,22 +15139,22 @@
         <v>19</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>593</v>
+        <v>170</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>594</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>595</v>
+        <v>566</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>595</v>
+        <v>545</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>19</v>
+        <v>476</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -15048,22 +15167,26 @@
         <v>19</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>189</v>
+        <v>134</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>596</v>
+        <v>477</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
+        <v>478</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>19</v>
       </c>
@@ -15087,13 +15210,13 @@
         <v>19</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>344</v>
+        <v>19</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>598</v>
+        <v>19</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>599</v>
+        <v>19</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>19</v>
@@ -15111,7 +15234,7 @@
         <v>19</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>595</v>
+        <v>479</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
@@ -15123,7 +15246,7 @@
         <v>19</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>19</v>
@@ -15132,18 +15255,18 @@
         <v>19</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>600</v>
+        <v>132</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>601</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>602</v>
+        <v>567</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>602</v>
+        <v>546</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15163,20 +15286,18 @@
         <v>19</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K112" t="s" s="2">
         <v>189</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>603</v>
+        <v>547</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>605</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>19</v>
@@ -15201,13 +15322,11 @@
         <v>19</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>606</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>607</v>
+        <v>549</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>19</v>
@@ -15225,7 +15344,7 @@
         <v>19</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>602</v>
+        <v>546</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>77</v>
@@ -15246,18 +15365,18 @@
         <v>19</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>608</v>
+        <v>19</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>609</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>610</v>
+        <v>568</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>610</v>
+        <v>569</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15280,17 +15399,15 @@
         <v>19</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>430</v>
+        <v>89</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>611</v>
+        <v>166</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>613</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>19</v>
@@ -15339,7 +15456,7 @@
         <v>19</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>610</v>
+        <v>168</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>77</v>
@@ -15348,10 +15465,10 @@
         <v>87</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>19</v>
@@ -15360,7 +15477,7 @@
         <v>19</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>614</v>
+        <v>170</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>19</v>
@@ -15368,21 +15485,21 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>615</v>
+        <v>570</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>615</v>
+        <v>571</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>19</v>
+        <v>147</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>19</v>
@@ -15394,15 +15511,17 @@
         <v>19</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>226</v>
+        <v>134</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N114" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>19</v>
@@ -15439,31 +15558,31 @@
         <v>19</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AC114" t="s" s="2">
-        <v>19</v>
+        <v>175</v>
       </c>
       <c r="AD114" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>169</v>
+        <v>19</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>19</v>
@@ -15480,10 +15599,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>616</v>
+        <v>572</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>616</v>
+        <v>573</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15503,19 +15622,23 @@
         <v>19</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>134</v>
+        <v>203</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>135</v>
+        <v>204</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="O115" t="s" s="2">
+        <v>207</v>
+      </c>
       <c r="P115" t="s" s="2">
         <v>19</v>
       </c>
@@ -15551,17 +15674,19 @@
         <v>19</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AC115" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="AD115" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>77</v>
@@ -15573,7 +15698,7 @@
         <v>19</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>19</v>
@@ -15582,22 +15707,20 @@
         <v>19</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>19</v>
+        <v>209</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>19</v>
+        <v>210</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>617</v>
+        <v>574</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="C116" t="s" s="2">
-        <v>618</v>
-      </c>
+        <v>575</v>
+      </c>
+      <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
         <v>19</v>
       </c>
@@ -15618,13 +15741,13 @@
         <v>19</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>619</v>
+        <v>89</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>620</v>
+        <v>166</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>621</v>
+        <v>167</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15675,19 +15798,19 @@
         <v>19</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>19</v>
@@ -15696,7 +15819,7 @@
         <v>19</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>19</v>
@@ -15704,23 +15827,21 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>622</v>
+        <v>576</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>623</v>
-      </c>
+        <v>577</v>
+      </c>
+      <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>19</v>
+        <v>147</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>19</v>
@@ -15732,15 +15853,17 @@
         <v>19</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>624</v>
+        <v>134</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>625</v>
+        <v>173</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="N117" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>19</v>
@@ -15777,16 +15900,16 @@
         <v>19</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="AC117" t="s" s="2">
-        <v>19</v>
+        <v>175</v>
       </c>
       <c r="AD117" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE117" t="s" s="2">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="AF117" t="s" s="2">
         <v>176</v>
@@ -15810,7 +15933,7 @@
         <v>19</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>19</v>
@@ -15818,45 +15941,45 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>627</v>
+        <v>578</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>627</v>
+        <v>579</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>441</v>
+        <v>19</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I118" t="s" s="2">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="J118" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>442</v>
+        <v>217</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>443</v>
+        <v>218</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>19</v>
@@ -15905,19 +16028,19 @@
         <v>19</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>444</v>
+        <v>221</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>19</v>
@@ -15926,18 +16049,18 @@
         <v>19</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>132</v>
+        <v>222</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>19</v>
+        <v>223</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>628</v>
+        <v>580</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>628</v>
+        <v>581</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15957,18 +16080,20 @@
         <v>19</v>
       </c>
       <c r="J119" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>154</v>
+        <v>226</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>629</v>
+        <v>227</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>19</v>
@@ -16017,7 +16142,7 @@
         <v>19</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>628</v>
+        <v>230</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>77</v>
@@ -16038,18 +16163,18 @@
         <v>19</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>160</v>
+        <v>231</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>631</v>
+        <v>232</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>632</v>
+        <v>582</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>632</v>
+        <v>583</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16057,7 +16182,7 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G120" t="s" s="2">
         <v>87</v>
@@ -16069,25 +16194,27 @@
         <v>19</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>330</v>
+        <v>107</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>633</v>
+        <v>235</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>634</v>
+        <v>236</v>
       </c>
       <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
+      <c r="O120" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>19</v>
       </c>
       <c r="Q120" s="2"/>
       <c r="R120" t="s" s="2">
-        <v>19</v>
+        <v>584</v>
       </c>
       <c r="S120" t="s" s="2">
         <v>19</v>
@@ -16129,7 +16256,7 @@
         <v>19</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>632</v>
+        <v>239</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>77</v>
@@ -16138,7 +16265,7 @@
         <v>87</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>19</v>
+        <v>240</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>99</v>
@@ -16150,18 +16277,18 @@
         <v>19</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>635</v>
+        <v>241</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>19</v>
+        <v>242</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>636</v>
+        <v>585</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>636</v>
+        <v>586</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16181,19 +16308,21 @@
         <v>19</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>637</v>
+        <v>245</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>638</v>
+        <v>246</v>
       </c>
       <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
+      <c r="O121" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>19</v>
       </c>
@@ -16217,13 +16346,13 @@
         <v>19</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>344</v>
+        <v>19</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>639</v>
+        <v>19</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>640</v>
+        <v>19</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>19</v>
@@ -16241,7 +16370,7 @@
         <v>19</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>636</v>
+        <v>248</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>77</v>
@@ -16250,7 +16379,7 @@
         <v>87</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>19</v>
+        <v>240</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>99</v>
@@ -16262,18 +16391,18 @@
         <v>19</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>641</v>
+        <v>249</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>642</v>
+        <v>250</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>643</v>
+        <v>587</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>643</v>
+        <v>588</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16293,19 +16422,23 @@
         <v>19</v>
       </c>
       <c r="J122" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>189</v>
+        <v>253</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>644</v>
+        <v>254</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
+        <v>255</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="O122" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="P122" t="s" s="2">
         <v>19</v>
       </c>
@@ -16329,13 +16462,13 @@
         <v>19</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>646</v>
+        <v>19</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>647</v>
+        <v>19</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>19</v>
@@ -16353,7 +16486,7 @@
         <v>19</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>643</v>
+        <v>258</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>77</v>
@@ -16374,18 +16507,18 @@
         <v>19</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>170</v>
+        <v>259</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>648</v>
+        <v>260</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>649</v>
+        <v>589</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>649</v>
+        <v>590</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16405,19 +16538,23 @@
         <v>19</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>330</v>
+        <v>226</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>650</v>
+        <v>263</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="O123" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P123" t="s" s="2">
         <v>19</v>
       </c>
@@ -16465,7 +16602,7 @@
         <v>19</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>649</v>
+        <v>267</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>77</v>
@@ -16486,29 +16623,29 @@
         <v>19</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>652</v>
+        <v>268</v>
       </c>
       <c r="AN123" t="s" s="2">
-        <v>653</v>
+        <v>269</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>654</v>
+        <v>591</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>654</v>
+        <v>550</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>19</v>
+        <v>551</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>19</v>
@@ -16517,16 +16654,16 @@
         <v>19</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>189</v>
+        <v>552</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>655</v>
+        <v>553</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>656</v>
+        <v>554</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16557,7 +16694,7 @@
       </c>
       <c r="Y124" s="2"/>
       <c r="Z124" t="s" s="2">
-        <v>657</v>
+        <v>592</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>19</v>
@@ -16575,13 +16712,13 @@
         <v>19</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>654</v>
+        <v>550</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>19</v>
@@ -16590,24 +16727,24 @@
         <v>99</v>
       </c>
       <c r="AK124" t="s" s="2">
-        <v>19</v>
+        <v>557</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>19</v>
+        <v>558</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>658</v>
+        <v>559</v>
       </c>
       <c r="AN124" t="s" s="2">
-        <v>659</v>
+        <v>560</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>660</v>
+        <v>593</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>660</v>
+        <v>593</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16627,19 +16764,19 @@
         <v>19</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>430</v>
+        <v>465</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>661</v>
+        <v>594</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>662</v>
+        <v>595</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>663</v>
+        <v>596</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -16689,7 +16826,7 @@
         <v>19</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>660</v>
+        <v>593</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>77</v>
@@ -16710,7 +16847,7 @@
         <v>19</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>664</v>
+        <v>597</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>19</v>
@@ -16718,10 +16855,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>665</v>
+        <v>598</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>665</v>
+        <v>598</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16830,10 +16967,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>666</v>
+        <v>599</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>666</v>
+        <v>599</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16944,14 +17081,14 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>667</v>
+        <v>600</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>667</v>
+        <v>600</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>441</v>
+        <v>476</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -16973,10 +17110,10 @@
         <v>134</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>442</v>
+        <v>477</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>443</v>
+        <v>478</v>
       </c>
       <c r="N128" t="s" s="2">
         <v>150</v>
@@ -17031,7 +17168,7 @@
         <v>19</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>444</v>
+        <v>479</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>77</v>
@@ -17060,21 +17197,21 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>668</v>
+        <v>601</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>668</v>
+        <v>601</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>19</v>
+        <v>602</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>19</v>
@@ -17083,16 +17220,16 @@
         <v>19</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>669</v>
+        <v>603</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>670</v>
+        <v>604</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>671</v>
+        <v>605</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17119,13 +17256,11 @@
         <v>19</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
-        <v>19</v>
+        <v>606</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>19</v>
@@ -17143,13 +17278,13 @@
         <v>19</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>668</v>
+        <v>601</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>19</v>
@@ -17158,24 +17293,24 @@
         <v>99</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>672</v>
+        <v>557</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>673</v>
+        <v>558</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>466</v>
+        <v>607</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>674</v>
+        <v>608</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>675</v>
+        <v>609</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>675</v>
+        <v>609</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17186,7 +17321,7 @@
         <v>77</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>19</v>
@@ -17198,17 +17333,15 @@
         <v>19</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>107</v>
+        <v>189</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>676</v>
+        <v>610</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>678</v>
-      </c>
+        <v>611</v>
+      </c>
+      <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>19</v>
@@ -17236,10 +17369,10 @@
         <v>111</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>679</v>
+        <v>612</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>680</v>
+        <v>613</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>19</v>
@@ -17257,13 +17390,13 @@
         <v>19</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>675</v>
+        <v>609</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>19</v>
@@ -17278,18 +17411,18 @@
         <v>19</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>681</v>
+        <v>170</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>19</v>
+        <v>614</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>682</v>
+        <v>615</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>682</v>
+        <v>615</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17300,7 +17433,7 @@
         <v>77</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>19</v>
@@ -17312,16 +17445,16 @@
         <v>19</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>189</v>
+        <v>616</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>683</v>
+        <v>617</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>684</v>
+        <v>618</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>685</v>
+        <v>619</v>
       </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
@@ -17347,13 +17480,13 @@
         <v>19</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>360</v>
+        <v>19</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>686</v>
+        <v>19</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>687</v>
+        <v>19</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>19</v>
@@ -17371,13 +17504,13 @@
         <v>19</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>682</v>
+        <v>615</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>19</v>
@@ -17392,7 +17525,7 @@
         <v>19</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>19</v>
+        <v>620</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>19</v>
@@ -17400,10 +17533,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>688</v>
+        <v>621</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>688</v>
+        <v>621</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17414,7 +17547,7 @@
         <v>77</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>19</v>
@@ -17426,16 +17559,20 @@
         <v>19</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>292</v>
+        <v>189</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>689</v>
+        <v>622</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="N132" s="2"/>
-      <c r="O132" s="2"/>
+        <v>623</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>625</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>19</v>
       </c>
@@ -17459,13 +17596,13 @@
         <v>19</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>19</v>
+        <v>395</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>19</v>
+        <v>626</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>19</v>
+        <v>627</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>19</v>
@@ -17483,13 +17620,13 @@
         <v>19</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>688</v>
+        <v>621</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>19</v>
@@ -17504,9 +17641,2493 @@
         <v>19</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>458</v>
+        <v>628</v>
       </c>
       <c r="AN132" t="s" s="2">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
+      <c r="P133" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="N134" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="N135" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N136" s="2"/>
+      <c r="O136" s="2"/>
+      <c r="P136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="N137" s="2"/>
+      <c r="O137" s="2"/>
+      <c r="P137" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AC137" s="2"/>
+      <c r="AD137" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN137" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="C138" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="D138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
+      <c r="P138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM138" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN138" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="C139" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="D139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="N139" s="2"/>
+      <c r="O139" s="2"/>
+      <c r="P139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q139" s="2"/>
+      <c r="R139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM139" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN139" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="E140" s="2"/>
+      <c r="F140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K140" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N140" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O140" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="P140" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q140" s="2"/>
+      <c r="R140" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S140" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK140" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL140" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM140" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN140" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G141" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K141" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="M141" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="N141" s="2"/>
+      <c r="O141" s="2"/>
+      <c r="P141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q141" s="2"/>
+      <c r="R141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ141" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL141" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM141" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AN141" t="s" s="2">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E142" s="2"/>
+      <c r="F142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G142" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K142" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L142" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="N142" s="2"/>
+      <c r="O142" s="2"/>
+      <c r="P142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q142" s="2"/>
+      <c r="R142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL142" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM142" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="AN142" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="C143" s="2"/>
+      <c r="D143" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E143" s="2"/>
+      <c r="F143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G143" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H143" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I143" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J143" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K143" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L143" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="N143" s="2"/>
+      <c r="O143" s="2"/>
+      <c r="P143" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q143" s="2"/>
+      <c r="R143" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S143" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T143" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U143" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V143" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W143" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X143" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="Y143" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="Z143" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="AA143" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB143" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF143" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="AG143" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH143" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI143" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ143" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK143" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL143" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM143" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="AN143" t="s" s="2">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G144" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H144" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I144" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J144" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K144" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="N144" s="2"/>
+      <c r="O144" s="2"/>
+      <c r="P144" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q144" s="2"/>
+      <c r="R144" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S144" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T144" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U144" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V144" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W144" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X144" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="Y144" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="Z144" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF144" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="AG144" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH144" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI144" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ144" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK144" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL144" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM144" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AN144" t="s" s="2">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="N145" s="2"/>
+      <c r="O145" s="2"/>
+      <c r="P145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM145" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="AN145" t="s" s="2">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E146" s="2"/>
+      <c r="F146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G146" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="N146" s="2"/>
+      <c r="O146" s="2"/>
+      <c r="P146" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q146" s="2"/>
+      <c r="R146" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S146" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y146" s="2"/>
+      <c r="Z146" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL146" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM146" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="AN146" t="s" s="2">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E147" s="2"/>
+      <c r="F147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K147" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="O147" s="2"/>
+      <c r="P147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q147" s="2"/>
+      <c r="R147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF147" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="AG147" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ147" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL147" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM147" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AN147" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E148" s="2"/>
+      <c r="F148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G148" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K148" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L148" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N148" s="2"/>
+      <c r="O148" s="2"/>
+      <c r="P148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q148" s="2"/>
+      <c r="R148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF148" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG148" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH148" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI148" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL148" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM148" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AN148" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="E149" s="2"/>
+      <c r="F149" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K149" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O149" s="2"/>
+      <c r="P149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q149" s="2"/>
+      <c r="R149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF149" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG149" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH149" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ149" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL149" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM149" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AN149" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="C150" s="2"/>
+      <c r="D150" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="E150" s="2"/>
+      <c r="F150" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H150" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I150" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J150" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K150" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L150" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N150" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O150" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="P150" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q150" s="2"/>
+      <c r="R150" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S150" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T150" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U150" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V150" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W150" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X150" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y150" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z150" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF150" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AG150" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH150" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI150" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ150" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK150" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL150" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM150" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN150" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="C151" s="2"/>
+      <c r="D151" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E151" s="2"/>
+      <c r="F151" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="G151" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H151" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J151" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K151" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="L151" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>706</v>
+      </c>
+      <c r="N151" s="2"/>
+      <c r="O151" s="2"/>
+      <c r="P151" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q151" s="2"/>
+      <c r="R151" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S151" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T151" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U151" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V151" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W151" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X151" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z151" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA151" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF151" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="AG151" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AH151" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI151" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ151" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK151" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="AL151" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="AM151" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AN151" t="s" s="2">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E152" s="2"/>
+      <c r="F152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G152" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H152" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I152" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J152" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K152" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="O152" s="2"/>
+      <c r="P152" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q152" s="2"/>
+      <c r="R152" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S152" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T152" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U152" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V152" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W152" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X152" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>715</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF152" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="AG152" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH152" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI152" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ152" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK152" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM152" t="s" s="2">
+        <v>716</v>
+      </c>
+      <c r="AN152" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="C153" s="2"/>
+      <c r="D153" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E153" s="2"/>
+      <c r="F153" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G153" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H153" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I153" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J153" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K153" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L153" t="s" s="2">
+        <v>718</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>720</v>
+      </c>
+      <c r="O153" s="2"/>
+      <c r="P153" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q153" s="2"/>
+      <c r="R153" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S153" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T153" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U153" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V153" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W153" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X153" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="Y153" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="Z153" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF153" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="AG153" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH153" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI153" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ153" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK153" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL153" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM153" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN153" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="C154" s="2"/>
+      <c r="D154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E154" s="2"/>
+      <c r="F154" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G154" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K154" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L154" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="M154" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="N154" s="2"/>
+      <c r="O154" s="2"/>
+      <c r="P154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q154" s="2"/>
+      <c r="R154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF154" t="s" s="2">
+        <v>723</v>
+      </c>
+      <c r="AG154" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH154" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ154" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL154" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM154" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AN154" t="s" s="2">
         <v>19</v>
       </c>
     </row>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T10:30:22+00:00</t>
+    <t>2024-11-12T12:40:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T12:40:22+00:00</t>
+    <t>2024-11-12T14:33:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:33:00+00:00</t>
+    <t>2024-11-12T14:36:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:36:04+00:00</t>
+    <t>2024-11-12T18:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:20:22+00:00</t>
+    <t>2024-11-12T18:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:30:34+00:00</t>
+    <t>2024-11-12T19:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:00:23+00:00</t>
+    <t>2024-11-12T19:16:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:16:24+00:00</t>
+    <t>2024-11-12T19:22:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:22:29+00:00</t>
+    <t>2024-11-14T14:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:59:39+00:00</t>
+    <t>2024-11-14T15:15:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -621,7 +621,7 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet/hl7-at-patientidentifier</t>
+    <t>http://terminology.hl7.org/ValueSet/v2-0203</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1934,7 +1934,7 @@
     <t>Code für den Typ der LKF Diagnose, der angibt ob es sich um eine Haupt- oder Nebendiagnose handelt</t>
   </si>
   <si>
-    <t>https://termgit.elga.gv.at/ValueSet-lkf-diagnose-typ.html</t>
+    <t>https://termgit.elga.gv.at/CodeSystem-lkf-diagnose-typ.html</t>
   </si>
   <si>
     <t>DG1-6 (Diagnosis Type)</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T15:15:53+00:00</t>
+    <t>2024-11-15T07:51:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T07:51:28+00:00</t>
+    <t>2024-11-15T09:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T09:58:51+00:00</t>
+    <t>2024-11-15T11:02:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T11:02:30+00:00</t>
+    <t>2024-11-15T19:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:27:47+00:00</t>
+    <t>2024-11-15T20:19:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T20:19:59+00:00</t>
+    <t>2024-11-17T19:53:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T19:53:01+00:00</t>
+    <t>2024-11-17T20:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:11:24+00:00</t>
+    <t>2024-11-20T22:25:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-20T22:25:32+00:00</t>
+    <t>2024-11-22T08:03:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-22T08:03:54+00:00</t>
+    <t>2024-12-12T14:30:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-13T08:39:47+00:00</t>
+    <t>2025-01-07T14:12:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:12:01+00:00</t>
+    <t>2025-01-07T14:17:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:17:45+00:00</t>
+    <t>2025-01-14T08:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:01:21+00:00</t>
+    <t>2025-01-14T08:16:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:16:01+00:00</t>
+    <t>2025-02-07T07:07:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1182,49 +1182,49 @@
     <t>Encounter.class.text</t>
   </si>
   <si>
-    <t>Encounter.class:Aufnahmeart</t>
-  </si>
-  <si>
-    <t>Aufnahmeart</t>
-  </si>
-  <si>
-    <t>http://example.org/ValueSet/moped-aufnahmeart-valueset</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.id</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.extension</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding.id</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding.extension</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding.system</t>
+    <t>Encounter.class:Aufnahmeart2</t>
+  </si>
+  <si>
+    <t>Aufnahmeart2</t>
+  </si>
+  <si>
+    <t>http://example.org/ValueSet/moped-aufnahmeart2-valueset</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.id</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.extension</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding.id</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding.extension</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding.system</t>
   </si>
   <si>
     <t>http://tbd.at/moped-ext-aufnahmeart</t>
   </si>
   <si>
-    <t>Encounter.class:Aufnahmeart.coding.version</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding.code</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding.display</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Encounter.class:Aufnahmeart.text</t>
+    <t>Encounter.class:Aufnahmeart2.coding.version</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding.code</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding.display</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Encounter.class:Aufnahmeart2.text</t>
   </si>
   <si>
     <t>Encounter.priority</t>
@@ -2063,20 +2063,20 @@
     <t>Encounter.admission.extension</t>
   </si>
   <si>
-    <t>Encounter.admission.extension:zugangsart</t>
-  </si>
-  <si>
-    <t>zugangsart</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-zugangsart}
+    <t>Encounter.admission.extension:aufnahmeart</t>
+  </si>
+  <si>
+    <t>aufnahmeart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-aufnahmeart}
 </t>
   </si>
   <si>
-    <t>Zugangsart</t>
-  </si>
-  <si>
-    <t>MOPED Extension für die Art des Zugangs.</t>
+    <t>Aufnahmeart</t>
+  </si>
+  <si>
+    <t>MOPED Extension für die Aufnahmeart.</t>
   </si>
   <si>
     <t>Encounter.admission.extension:transportart</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T07:07:15+00:00</t>
+    <t>2025-02-07T10:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T10:07:52+00:00</t>
+    <t>2025-02-10T08:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:30:06+00:00</t>
+    <t>2025-02-10T08:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:38:31+00:00</t>
+    <t>2025-02-11T11:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDEncounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:17:52+00:00</t>
+    <t>2025-02-11T16:50:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
